--- a/tame_output/ON/bt/strategyON_20240511.xlsx
+++ b/tame_output/ON/bt/strategyON_20240511.xlsx
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.531150440580726</v>
+        <v>-4.530991498081999</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8810867519335948</v>
+        <v>0.8811503289330855</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4311857081094327</v>
+        <v>-0.4309538167724878</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.435191927613973</v>
+        <v>2.43533106241614</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240511.xlsx
+++ b/tame_output/ON/bt/strategyON_20240511.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.6%</t>
+          <t>112.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>133.6%</t>
+          <t>132.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.4%</t>
+          <t>-54.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-614.7%</t>
+          <t>-586.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.6%</t>
+          <t>-39.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,22 +1165,22 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-288.1%</t>
+          <t>-276.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-22.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-130.1%</t>
+          <t>-133.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-267.1%</t>
+          <t>-257.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-202.5%</t>
+          <t>-196.5%</t>
         </is>
       </c>
     </row>
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.530991498081999</v>
+        <v>-4.247120113005064</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8811503289330855</v>
+        <v>0.9946988829638594</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4309538167724878</v>
+        <v>-0.3305534877022266</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.43533106241614</v>
+        <v>2.495571259858297</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240511.xlsx
+++ b/tame_output/ON/bt/strategyON_20240511.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,42 +824,42 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-42.2%</t>
+          <t>-11.4%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.4%</t>
+          <t>132.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-29.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-196.5%</t>
+          <t>-146.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1960"/>
+  <dimension ref="A1:G1961"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.898448015050919</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
@@ -46641,6 +46641,29 @@
       </c>
       <c r="G1960" t="n">
         <v>2.495571259858297</v>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" s="2" t="n">
+        <v>45423</v>
+      </c>
+      <c r="B1961" t="n">
+        <v>3.905502420619522</v>
+      </c>
+      <c r="C1961" t="n">
+        <v>3.001872222535171</v>
+      </c>
+      <c r="D1961" t="n">
+        <v>-4.247120113005064</v>
+      </c>
+      <c r="E1961" t="n">
+        <v>0.9946988829638594</v>
+      </c>
+      <c r="F1961" t="n">
+        <v>-0.3305534877022266</v>
+      </c>
+      <c r="G1961" t="n">
+        <v>2.994936019521539</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240511.xlsx
+++ b/tame_output/ON/bt/strategyON_20240511.xlsx
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.78291895796342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353074</v>
+        <v>3.764614304353076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544783</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712294</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837686</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349967</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972341</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866537614594</v>
+        <v>3.818665376145942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009952</v>
+        <v>3.843270952009954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>3.845043810966262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046997</v>
+        <v>3.791269976046999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144517</v>
+        <v>3.762643902144519</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.729142822900696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473602</v>
+        <v>3.743216620473603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978371</v>
+        <v>3.714175563978372</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887705</v>
+        <v>3.710903155887706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675903</v>
+        <v>3.746038950675905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695448</v>
+        <v>3.765020747695449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581293</v>
+        <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212298</v>
+        <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786045</v>
+        <v>3.752023923786047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968863</v>
+        <v>3.689594264968865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175323</v>
+        <v>3.643066046175325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271273519927</v>
+        <v>3.682712735199272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73300886566077</v>
+        <v>3.733008865660771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383425</v>
+        <v>3.741170494383427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002486</v>
+        <v>3.751143622002488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263904</v>
+        <v>3.741324873263905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481238</v>
+        <v>3.75072580148124</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452233</v>
+        <v>3.716988143452235</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702303297954</v>
+        <v>3.737023032979542</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230807</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.905502420619522</v>
+        <v>3.905502420619523</v>
       </c>
       <c r="C1961" t="n">
         <v>3.001872222535171</v>

--- a/tame_output/ON/bt/strategyON_20240511.xlsx
+++ b/tame_output/ON/bt/strategyON_20240511.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>58.5%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-22.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.9%</t>
+          <t>113.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.3%</t>
+          <t>132.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-54.7%</t>
+          <t>-52.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.7%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.4%</t>
+          <t>444.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-586.3%</t>
+          <t>-597.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-40.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-46.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.8%</t>
+          <t>-281.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.1%</t>
+          <t>-20.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-133.1%</t>
+          <t>-196.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-257.0%</t>
+          <t>-249.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-146.5%</t>
+          <t>-157.8%</t>
         </is>
       </c>
     </row>
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.09781873856928</v>
+        <v>-9.903726080461677</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9075705809264289</v>
+        <v>-0.829933517683386</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.236849568239943</v>
+        <v>-2.042756910132336</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.789803597871067</v>
+        <v>1.906259192735631</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.09412781361287</v>
+        <v>-9.900035155505266</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9060942109438641</v>
+        <v>-0.8284571477008216</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.236849568239943</v>
+        <v>-2.042756910132336</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.789803597871067</v>
+        <v>1.906259192735631</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.29838598894274</v>
+        <v>-10.10429333083513</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.982284283957167</v>
+        <v>-0.904647220714125</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.364488512853932</v>
+        <v>-2.170395854746325</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.718733428221316</v>
+        <v>1.83518902308588</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.51642376057391</v>
+        <v>-10.32233110246631</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.065016838125203</v>
+        <v>-0.9873797748821596</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.539259280949831</v>
+        <v>-2.345166622842224</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.618353521848213</v>
+        <v>1.734809116712777</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.44295392890647</v>
+        <v>-10.24886127079886</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.020257203964801</v>
+        <v>-0.9426201407217585</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.465789449282382</v>
+        <v>-2.271696791174775</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.677807122342103</v>
+        <v>1.794262717206667</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.61807834629301</v>
+        <v>-10.4239856881854</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.075751750171902</v>
+        <v>-0.9981146869288597</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.640913866668926</v>
+        <v>-2.446821208561319</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.587287692657693</v>
+        <v>1.703743287522258</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.8525304403075</v>
+        <v>-10.65843778219989</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.176751752679294</v>
+        <v>-1.099114689436251</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.640913866668926</v>
+        <v>-2.446821208561319</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.580068527756097</v>
+        <v>1.696524122620662</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.14033428484474</v>
+        <v>-10.94624162673713</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.298545481268166</v>
+        <v>-1.220908418025123</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.928717711206164</v>
+        <v>-2.734625053098557</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.400714030259778</v>
+        <v>1.517169625124343</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.37015873200856</v>
+        <v>-11.17606607390096</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.38935947029514</v>
+        <v>-1.311722407052097</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.091365248276325</v>
+        <v>-2.897272590168718</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.304241297856238</v>
+        <v>1.420696892720802</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.60218765174482</v>
+        <v>-11.40809499363722</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.47947730956053</v>
+        <v>-1.401840246317487</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.153377945464748</v>
+        <v>-2.959285287357141</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.269727408172299</v>
+        <v>1.386183003036863</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.55017213777601</v>
+        <v>-11.3560794796684</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.454680768286603</v>
+        <v>-1.377043705043561</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.153377945464748</v>
+        <v>-2.959285287357141</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.2737177438587</v>
+        <v>1.390173338723264</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.69184397950013</v>
+        <v>-11.49775132139252</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.512824731874993</v>
+        <v>-1.435187668631951</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.153377945464748</v>
+        <v>-2.959285287357141</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.272242516959958</v>
+        <v>1.388698111824522</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.6422531350753</v>
+        <v>-11.44816047696769</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.477934983940187</v>
+        <v>-1.400297920697144</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.103787101039914</v>
+        <v>-2.909694442932307</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.317050433779731</v>
+        <v>1.433506028644295</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.4431010278382</v>
+        <v>-11.24900836973059</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.41132527469203</v>
+        <v>-1.333688211448988</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.938464575090101</v>
+        <v>-2.744371916982494</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.403192815702936</v>
+        <v>1.5196484105675</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.21725587511879</v>
+        <v>-11.02316321701118</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.311408140568058</v>
+        <v>-1.233771077325015</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.896537899502937</v>
+        <v>-2.70244524139533</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.437927894091443</v>
+        <v>1.554383488956007</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.0926772187812</v>
+        <v>-10.89858456067359</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.260437533476962</v>
+        <v>-1.182800470233919</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.896537899502937</v>
+        <v>-2.70244524139533</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.439067038647502</v>
+        <v>1.555522633512066</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.14557250682548</v>
+        <v>-10.95147984871788</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.278961874532569</v>
+        <v>-1.201324811289527</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.891582553414491</v>
+        <v>-2.697489895306884</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.444674020462677</v>
+        <v>1.561129615327241</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.86166377589673</v>
+        <v>-10.66757111778913</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.159664677922433</v>
+        <v>-1.08202761467939</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.891582553414491</v>
+        <v>-2.697489895306884</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.450407724701313</v>
+        <v>1.566863319565877</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.79029738328709</v>
+        <v>-10.59620472517948</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.14085538327244</v>
+        <v>-1.063218320029397</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.820216160804843</v>
+        <v>-2.626123502697236</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.483490297873237</v>
+        <v>1.599945892737801</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.52646051608302</v>
+        <v>-10.33236785797541</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.045204117703719</v>
+        <v>-0.9675670544606763</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.820216160804843</v>
+        <v>-2.626123502697236</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.473606816560329</v>
+        <v>1.590062411424894</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.25921871521462</v>
+        <v>-10.06512605710701</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9401419578557335</v>
+        <v>-0.8625048946126905</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.820216160804843</v>
+        <v>-2.626123502697236</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.471772256060956</v>
+        <v>1.58822785092552</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.16131167653813</v>
+        <v>-9.967219018430521</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9012794573585983</v>
+        <v>-0.8236423941155553</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.752230410944287</v>
+        <v>-2.55813775283668</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.512263391003829</v>
+        <v>1.628718985868393</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.13735813556217</v>
+        <v>-9.943265477454563</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8910295348227213</v>
+        <v>-0.8133924715796788</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.728276869968329</v>
+        <v>-2.534184211860722</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.527304021734897</v>
+        <v>1.643759616599461</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.873298197239373</v>
+        <v>-9.679205539131766</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7986658756553551</v>
+        <v>-0.7210288124123121</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.464216931645533</v>
+        <v>-2.270124273537926</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.672479668566822</v>
+        <v>1.788935263431386</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.166218573734536</v>
+        <v>-8.972125915626929</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5186210599137207</v>
+        <v>-0.4409839966706781</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.464216931645533</v>
+        <v>-2.270124273537926</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.669692634906521</v>
+        <v>1.786148229771086</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.126034275368346</v>
+        <v>-8.931941617260739</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5022037166794031</v>
+        <v>-0.4245666534363606</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.424032633279342</v>
+        <v>-2.229939975171735</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.694146837814077</v>
+        <v>1.810602432678641</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.045964479830541</v>
+        <v>-8.851871821722934</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4708089772435247</v>
+        <v>-0.3931719140004817</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.343962837741538</v>
+        <v>-2.149870179633931</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.741555536357517</v>
+        <v>1.858011131222081</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.812483257600942</v>
+        <v>-8.635847115277619</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3694920595138322</v>
+        <v>-0.298837602584503</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.11048161551194</v>
+        <v>-1.933845473188615</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.889568698533128</v>
+        <v>1.995550383927123</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255787</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.632774727457068</v>
+        <v>-8.456138585133745</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3005008577692423</v>
+        <v>-0.229846400839913</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.053310111349244</v>
+        <v>-1.876673969025919</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.920979390717787</v>
+        <v>2.026961076111782</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.500499253826181</v>
+        <v>-8.323863111502858</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2522231815698603</v>
+        <v>-0.1815687246405311</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.921034637718357</v>
+        <v>-1.744398495395032</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.995712161643346</v>
+        <v>2.101693847037341</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.309899579153027</v>
+        <v>-8.133263436829704</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.173168251012962</v>
+        <v>-0.1025137940836327</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.730434963045204</v>
+        <v>-1.553798820721879</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.112887027134874</v>
+        <v>2.218868712528869</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.060899780469446</v>
+        <v>-7.884263638146123</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.06066199031587116</v>
+        <v>0.009992466613458095</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.730434963045204</v>
+        <v>-1.553798820721879</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.125793368358533</v>
+        <v>2.231775053752528</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.166489770242551</v>
+        <v>-7.989853627919228</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2308739158243314</v>
+        <v>-0.1602194588950021</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.836024952818309</v>
+        <v>-1.659388810494984</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.934463444895451</v>
+        <v>2.040445130289446</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.185224672361148</v>
+        <v>-8.008588530037825</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1898235347946837</v>
+        <v>-0.1191690778653545</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.836024952818309</v>
+        <v>-1.659388810494984</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.983007786772538</v>
+        <v>2.088989472166533</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180811</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.037284630953549</v>
+        <v>-7.860648488630225</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2505264409198116</v>
+        <v>-0.1798719839904823</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.815704036909751</v>
+        <v>-1.639067894586426</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.875321413629505</v>
+        <v>1.9813030990235</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879204</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.013055994564576</v>
+        <v>-7.836419852241253</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2495489726177009</v>
+        <v>-0.1788945156883717</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.791475400520779</v>
+        <v>-1.614839258197454</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.88114460920941</v>
+        <v>1.987126294603405</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.969507587793886</v>
+        <v>-7.792871445470563</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2390902220045179</v>
+        <v>-0.1684357650751886</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.791475400520779</v>
+        <v>-1.614839258197454</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.874183997114317</v>
+        <v>1.980165682508312</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78291895796342</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.727359194340027</v>
+        <v>-7.550723052016704</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1277685102418316</v>
+        <v>-0.0571140533125023</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.791475400520779</v>
+        <v>-1.614839258197454</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.88864635149546</v>
+        <v>1.994628036889455</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.664129822571679</v>
+        <v>-7.487493680248356</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1079446410752971</v>
+        <v>-0.03729018414596785</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.791475400520779</v>
+        <v>-1.614839258197454</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.883178471954655</v>
+        <v>1.98916015734865</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.540838687754548</v>
+        <v>-7.364202545431225</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.06113009313786799</v>
+        <v>0.009524363791461266</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.668184265703649</v>
+        <v>-1.491548123380324</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.95465124685551</v>
+        <v>2.060632932249505</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.519689488851105</v>
+        <v>-7.343053346527782</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.04496943533916564</v>
+        <v>0.02568502159016361</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.647035066800205</v>
+        <v>-1.47039892447688</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.975041744434901</v>
+        <v>2.081023429828896</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.275924046867661</v>
+        <v>-7.099287904544338</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.04831744980126285</v>
+        <v>0.1189719067305921</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.647035066800205</v>
+        <v>-1.47039892447688</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.970822452781952</v>
+        <v>2.076804138175947</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.011895979674401</v>
+        <v>-6.835259837351078</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1560529905985826</v>
+        <v>0.2267074475279118</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.445169667984252</v>
+        <v>-1.268533525660927</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.09406600599154</v>
+        <v>2.200047691385535</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749186</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.762045585725327</v>
+        <v>-6.585409443402003</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2487352231619147</v>
+        <v>0.3193896800912439</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.445169667984252</v>
+        <v>-1.268533525660927</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.086808080975242</v>
+        <v>2.192789766369237</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481499</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.586153493257894</v>
+        <v>-6.409517350934571</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3226911836695363</v>
+        <v>0.3933456405988656</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.445169667984252</v>
+        <v>-1.268533525660927</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.090407204495891</v>
+        <v>2.196388889889886</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862989</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.414707030235431</v>
+        <v>-6.238070887912108</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4045972749330753</v>
+        <v>0.4752517318624045</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.273723204961788</v>
+        <v>-1.097087062638463</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.206602588363922</v>
+        <v>2.312584273757917</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102783</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.189674030566608</v>
+        <v>-6.013037888243285</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4936309524169014</v>
+        <v>0.5642854093462306</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.048690205292965</v>
+        <v>-0.8720540629696406</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.340642865781513</v>
+        <v>2.446624551175508</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353076</v>
+        <v>3.764614304353074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.975039652930201</v>
+        <v>-5.798403510606878</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5841795045257818</v>
+        <v>0.6548339614551111</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8340558276565586</v>
+        <v>-0.6574196853332338</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.474118293417674</v>
+        <v>2.58009997881167</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.882039611724303</v>
+        <v>-5.70540346940098</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6025737797919364</v>
+        <v>0.6732282367212656</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8340558276565586</v>
+        <v>-0.6574196853332338</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.45531255220147</v>
+        <v>2.561294237595465</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.641609114919443</v>
+        <v>-5.46497297259612</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7004890551387581</v>
+        <v>0.7711435120680874</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5936253308516983</v>
+        <v>-0.4169891885283735</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.601313926909264</v>
+        <v>2.707295612303259</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.569366546748248</v>
+        <v>-5.392730404424925</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7333153962420562</v>
+        <v>0.8039698531713855</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5936253308516983</v>
+        <v>-0.4169891885283735</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.605243240744084</v>
+        <v>2.711224926138079</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.822323422349967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.453426697123063</v>
+        <v>-5.27679055479974</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7803699200094703</v>
+        <v>0.8510243769387995</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5168035998355744</v>
+        <v>-0.3401674575122496</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.652014863271098</v>
+        <v>2.757996548665093</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.2107711086999</v>
+        <v>-5.034134966376577</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8744302265987289</v>
+        <v>0.9450846835280582</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5168035998355744</v>
+        <v>-0.3401674575122496</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.649012934491092</v>
+        <v>2.754994619885087</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145942</v>
+        <v>3.81866537614594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.990750310662889</v>
+        <v>-4.814114168339566</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9640175828241473</v>
+        <v>1.034672039753477</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3755837547675942</v>
+        <v>-0.1989476124442694</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.735323878542494</v>
+        <v>2.841305563936489</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009954</v>
+        <v>3.843270952009952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.857882621599612</v>
+        <v>-4.681246479276289</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.033058841251282</v>
+        <v>1.103713298180611</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3755837547675942</v>
+        <v>-0.1989476124442694</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.751218061344317</v>
+        <v>2.857199746738312</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966262</v>
+        <v>3.845043810966259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.698367518080242</v>
+        <v>-4.521731375756919</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.098010727099331</v>
+        <v>1.168665184028661</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2160686512482243</v>
+        <v>-0.03943250892489947</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.848072967896241</v>
+        <v>2.954054653290236</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046999</v>
+        <v>3.791269976046996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.553695372980505</v>
+        <v>-4.377059230657181</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.165967687700666</v>
+        <v>1.236622144629995</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.07139650614848686</v>
+        <v>0.1052396361748379</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.944964357517523</v>
+        <v>3.050946042911518</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412106</v>
+        <v>3.735835647412103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.613570200338197</v>
+        <v>-4.436934058014874</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.128055248159015</v>
+        <v>1.198709705088344</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.131271333506179</v>
+        <v>0.04536480881714583</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.895076952504334</v>
+        <v>3.001058637898329</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144519</v>
+        <v>3.762643902144516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.526770702559189</v>
+        <v>-4.350134560235865</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.185175540593185</v>
+        <v>1.255829997522514</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.131271333506179</v>
+        <v>0.04536480881714583</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.9174774458269</v>
+        <v>3.023459131220895</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900696</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.529240409020995</v>
+        <v>-4.352604266697671</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.184260059381874</v>
+        <v>1.254914516311203</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1337410399679851</v>
+        <v>0.04289510235533966</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.916068023323228</v>
+        <v>3.022049708717224</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473603</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.597610595345005</v>
+        <v>-4.420974453021682</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.167918907326972</v>
+        <v>1.238573364256301</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1244653409317702</v>
+        <v>0.05217080139155461</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.93264036521966</v>
+        <v>3.038622050613654</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978372</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.476194165718528</v>
+        <v>-4.299558023395205</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.206922187809454</v>
+        <v>1.277576644738783</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1244653409317702</v>
+        <v>0.05217080139155461</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.923077073851551</v>
+        <v>3.029058759245546</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887706</v>
+        <v>3.710903155887703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.507187325047234</v>
+        <v>-4.33055118272391</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.019234489118359</v>
+        <v>1.089888946047688</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1244653409317702</v>
+        <v>0.05217080139155461</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.747786638891938</v>
+        <v>2.853768324285932</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675905</v>
+        <v>3.746038950675901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.331713065254764</v>
+        <v>-4.155076922931441</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.093991425027134</v>
+        <v>1.164645881956464</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1244653409317702</v>
+        <v>0.05217080139155461</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.752353870883725</v>
+        <v>2.85833555627772</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695449</v>
+        <v>3.765020747695446</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.442649317896013</v>
+        <v>-4.26601317557269</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.025358952731842</v>
+        <v>1.096013409661171</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1244653409317702</v>
+        <v>0.05217080139155461</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.728095899644932</v>
+        <v>2.834077585038927</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581294</v>
+        <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.645675895439246</v>
+        <v>-4.469039753115923</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9472797069344541</v>
+        <v>1.017934163863783</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3274919184750036</v>
+        <v>-0.1508557761516788</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.609411338338898</v>
+        <v>2.715393023732893</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734163</v>
+        <v>3.78434037673416</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.487750296503953</v>
+        <v>-4.31111415418063</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.020622332940704</v>
+        <v>1.091276789870033</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3274919184750036</v>
+        <v>-0.1508557761516788</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.61958372477103</v>
+        <v>2.725565410165025</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869463822123</v>
+        <v>3.786946382212296</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.636071550315082</v>
+        <v>-4.459435407991759</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9562401019901126</v>
+        <v>1.026894558919442</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3274919184750036</v>
+        <v>-0.1508557761516788</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.614529995344891</v>
+        <v>2.720511680738885</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786047</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.637254634966142</v>
+        <v>-4.460618492642819</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9475426435742138</v>
+        <v>1.018197100503543</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3331349669415151</v>
+        <v>-0.1564988246181903</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.602919941709509</v>
+        <v>2.708901627103504</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273192</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.514126927972059</v>
+        <v>-4.337490785648736</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9973455994049487</v>
+        <v>1.068000056334278</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3331349669415151</v>
+        <v>-0.1564988246181903</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.603471814742611</v>
+        <v>2.709453500136606</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279502</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.4213164465212</v>
+        <v>-4.244680304197876</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9637424838766582</v>
+        <v>1.034396940805987</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2403244854906558</v>
+        <v>-0.06368834316733096</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.588430795504492</v>
+        <v>2.694412480898487</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030429</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.37275339430017</v>
+        <v>-4.196117251976847</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9850411806896711</v>
+        <v>1.055695637619</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1917614332696256</v>
+        <v>-0.01512529094630077</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.619442102761711</v>
+        <v>2.725423788155706</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942741</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.26008217606392</v>
+        <v>-4.083446033740596</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.025185376495894</v>
+        <v>1.095839833425223</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.07909021503337538</v>
+        <v>0.09754592728994943</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.682120542215184</v>
+        <v>2.788102227609179</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268539</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.147705174881247</v>
+        <v>-3.971069032557924</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.07562747279963</v>
+        <v>1.146281929728959</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.07909021503337538</v>
+        <v>0.09754592728994943</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.687611838045851</v>
+        <v>2.793593523439846</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968865</v>
+        <v>3.689594264968861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.345939743767977</v>
+        <v>-4.169303601444654</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.007830847013477</v>
+        <v>1.078485303942806</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.277324783920106</v>
+        <v>-0.1006886415967811</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.580168298482352</v>
+        <v>2.686149983876347</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175325</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.428941024793256</v>
+        <v>-4.252304882469933</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8129860546040188</v>
+        <v>0.8836405115333481</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2958956684472797</v>
+        <v>-0.1192595261239549</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.407381487766701</v>
+        <v>2.513363173160696</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199272</v>
+        <v>3.682712735199268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.26974675273668</v>
+        <v>-4.093110610413357</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9968134241458553</v>
+        <v>1.067467881075185</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2958956684472797</v>
+        <v>-0.1192595261239549</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.527531148485907</v>
+        <v>2.633512833879902</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660771</v>
+        <v>3.733008865660768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.356345335717783</v>
+        <v>-4.179709193394459</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9766870170557369</v>
+        <v>1.047341473985066</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2958956684472797</v>
+        <v>-0.1192595261239549</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.54204417458823</v>
+        <v>2.648025859982225</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383427</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.317961673159632</v>
+        <v>-4.141325530836308</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9894599234213661</v>
+        <v>1.060114380350695</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2575120058891285</v>
+        <v>-0.08087586356580373</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.562493813465489</v>
+        <v>2.668475498859484</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002488</v>
+        <v>3.751143622002484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.140845343124465</v>
+        <v>-3.964209200801142</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.057035484280735</v>
+        <v>1.127689941210064</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2575120058891285</v>
+        <v>-0.08087586356580373</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.559222842310791</v>
+        <v>2.665204527704786</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263905</v>
+        <v>3.741324873263902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.111143219148172</v>
+        <v>-3.934507076824849</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.069599725633165</v>
+        <v>1.140254182562494</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2619821311044419</v>
+        <v>-0.0853459887811171</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.557224158943516</v>
+        <v>2.663205844337511</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.75072580148124</v>
+        <v>3.750725801481236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.931767797909404</v>
+        <v>-3.755131655586081</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.135136869435087</v>
+        <v>1.205791326364416</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1052053729337232</v>
+        <v>0.07143076938960158</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.645077189152362</v>
+        <v>2.751058874546357</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452235</v>
+        <v>3.716988143452231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.97678201143001</v>
+        <v>-3.800145869106687</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.097938639358434</v>
+        <v>1.168593096287763</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1355542682483278</v>
+        <v>0.04108187407499697</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.607675307295189</v>
+        <v>2.713656992689184</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979542</v>
+        <v>3.737023032979538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.243786521702446</v>
+        <v>-4.067150379379123</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9968283975884054</v>
+        <v>1.067482854517735</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3299173062912764</v>
+        <v>-0.1532811639679516</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.496749046808366</v>
+        <v>2.60273073220236</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230807</v>
+        <v>3.702305879230804</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.247120113005064</v>
+        <v>-4.355937599838038</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9946988829638594</v>
+        <v>0.9511718882306699</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3305534877022266</v>
+        <v>-0.254367284066952</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.495571259858297</v>
+        <v>2.541282982039462</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.905502420619523</v>
+        <v>3.865304099770293</v>
       </c>
       <c r="C1961" t="n">
-        <v>3.001872222535171</v>
+        <v>2.888901268509926</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.247120113005064</v>
+        <v>-4.355937599838038</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9946988829638594</v>
+        <v>0.9511718882306699</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3305534877022266</v>
+        <v>-0.254367284066952</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.994936019521539</v>
+        <v>2.881965065496294</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240511.xlsx
+++ b/tame_output/ON/bt/strategyON_20240511.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-78.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.1%</t>
+          <t>113.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.5%</t>
+          <t>444.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-597.2%</t>
+          <t>-595.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-46.3%</t>
+          <t>-56.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-281.1%</t>
+          <t>-280.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-26.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-196.2%</t>
+          <t>-177.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-249.4%</t>
+          <t>-247.3%</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.903726080461677</v>
+        <v>-9.900257016592157</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.829933517683386</v>
+        <v>-0.8285458921355775</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.042756910132336</v>
+        <v>-2.039287846262815</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.906259192735631</v>
+        <v>1.908340631057344</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.900035155505266</v>
+        <v>-9.896566091635746</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8284571477008216</v>
+        <v>-0.8270695221530135</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.042756910132336</v>
+        <v>-2.039287846262815</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.906259192735631</v>
+        <v>1.908340631057344</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.10429333083513</v>
+        <v>-10.10082426696561</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.904647220714125</v>
+        <v>-0.9032595951663165</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.170395854746325</v>
+        <v>-2.166926790876804</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.83518902308588</v>
+        <v>1.837270461407593</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.32233110246631</v>
+        <v>-10.31886203859679</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9873797748821596</v>
+        <v>-0.9859921493343511</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.345166622842224</v>
+        <v>-2.341697558972703</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.734809116712777</v>
+        <v>1.736890555034489</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.24886127079886</v>
+        <v>-10.24539220692934</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9426201407217585</v>
+        <v>-0.9412325151739509</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.271696791174775</v>
+        <v>-2.268227727305255</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.794262717206667</v>
+        <v>1.796344155528379</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.4239856881854</v>
+        <v>-10.42051662431588</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9981146869288597</v>
+        <v>-0.9967270613810513</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.446821208561319</v>
+        <v>-2.443352144691799</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.703743287522258</v>
+        <v>1.70582472584397</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.65843778219989</v>
+        <v>-10.65496871833037</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.099114689436251</v>
+        <v>-1.097727063888443</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.446821208561319</v>
+        <v>-2.443352144691799</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.696524122620662</v>
+        <v>1.698605560942374</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.94624162673713</v>
+        <v>-10.94277256286761</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.220908418025123</v>
+        <v>-1.219520792477315</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.734625053098557</v>
+        <v>-2.731155989229037</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.517169625124343</v>
+        <v>1.519251063446055</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.17606607390096</v>
+        <v>-11.17259701003143</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.311722407052097</v>
+        <v>-1.310334781504288</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.897272590168718</v>
+        <v>-2.893803526299197</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.420696892720802</v>
+        <v>1.422778331042515</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.40809499363722</v>
+        <v>-11.4046259297677</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.401840246317487</v>
+        <v>-1.400452620769678</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.959285287357141</v>
+        <v>-2.95581622348762</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.386183003036863</v>
+        <v>1.388264441358576</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.3560794796684</v>
+        <v>-11.35261041579888</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.377043705043561</v>
+        <v>-1.375656079495752</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.959285287357141</v>
+        <v>-2.95581622348762</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.390173338723264</v>
+        <v>1.392254777044976</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.49775132139252</v>
+        <v>-11.494282257523</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.435187668631951</v>
+        <v>-1.433800043084142</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.959285287357141</v>
+        <v>-2.95581622348762</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.388698111824522</v>
+        <v>1.390779550146235</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.44816047696769</v>
+        <v>-11.44469141309817</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.400297920697144</v>
+        <v>-1.398910295149336</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.909694442932307</v>
+        <v>-2.906225379062787</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.433506028644295</v>
+        <v>1.435587466966007</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.24900836973059</v>
+        <v>-11.24553930586107</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.333688211448988</v>
+        <v>-1.33230058590118</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.744371916982494</v>
+        <v>-2.740902853112973</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.5196484105675</v>
+        <v>1.521729848889212</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.02316321701118</v>
+        <v>-11.01969415314166</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.233771077325015</v>
+        <v>-1.232383451777207</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.70244524139533</v>
+        <v>-2.69897617752581</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.554383488956007</v>
+        <v>1.556464927277719</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.89858456067359</v>
+        <v>-10.89511549680407</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.182800470233919</v>
+        <v>-1.181412844686112</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.70244524139533</v>
+        <v>-2.69897617752581</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.555522633512066</v>
+        <v>1.557604071833778</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.95147984871788</v>
+        <v>-10.94801078484836</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.201324811289527</v>
+        <v>-1.199937185741718</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.697489895306884</v>
+        <v>-2.694020831437363</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.561129615327241</v>
+        <v>1.563211053648953</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.66757111778913</v>
+        <v>-10.66410205391961</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.08202761467939</v>
+        <v>-1.080639989131583</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.697489895306884</v>
+        <v>-2.694020831437363</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.566863319565877</v>
+        <v>1.56894475788759</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.59620472517948</v>
+        <v>-10.59273566130996</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.063218320029397</v>
+        <v>-1.061830694481588</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.626123502697236</v>
+        <v>-2.622654438827716</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.599945892737801</v>
+        <v>1.602027331059513</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.33236785797541</v>
+        <v>-10.32889879410589</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9675670544606763</v>
+        <v>-0.9661794289128678</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.626123502697236</v>
+        <v>-2.622654438827716</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.590062411424894</v>
+        <v>1.592143849746606</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.06512605710701</v>
+        <v>-10.06165699323749</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8625048946126905</v>
+        <v>-0.861117269064883</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.626123502697236</v>
+        <v>-2.622654438827716</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.58822785092552</v>
+        <v>1.590309289247232</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.967219018430521</v>
+        <v>-9.963749954561001</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8236423941155553</v>
+        <v>-0.8222547685677473</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.55813775283668</v>
+        <v>-2.554668688967159</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.628718985868393</v>
+        <v>1.630800424190105</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.943265477454563</v>
+        <v>-9.939796413585043</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8133924715796788</v>
+        <v>-0.8120048460318707</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.534184211860722</v>
+        <v>-2.530715147991202</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.643759616599461</v>
+        <v>1.645841054921173</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.679205539131766</v>
+        <v>-9.675736475262246</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7210288124123121</v>
+        <v>-0.7196411868645041</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.270124273537926</v>
+        <v>-2.266655209668406</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.788935263431386</v>
+        <v>1.791016701753099</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.972125915626929</v>
+        <v>-8.968656851757409</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4409839966706781</v>
+        <v>-0.4395963711228701</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.270124273537926</v>
+        <v>-2.266655209668406</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.786148229771086</v>
+        <v>1.788229668092798</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.931941617260739</v>
+        <v>-8.928472553391218</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4245666534363606</v>
+        <v>-0.4231790278885526</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.229939975171735</v>
+        <v>-2.226470911302215</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.810602432678641</v>
+        <v>1.812683871000354</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.851871821722934</v>
+        <v>-8.848402757853414</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3931719140004817</v>
+        <v>-0.3917842884526737</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.149870179633931</v>
+        <v>-2.146401115764411</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.858011131222081</v>
+        <v>1.860092569543793</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.635847115277619</v>
+        <v>-8.614921535623814</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.298837602584503</v>
+        <v>-0.2904673707229817</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.933845473188615</v>
+        <v>-1.912919893534812</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.995550383927123</v>
+        <v>2.008105731719405</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.456138585133745</v>
+        <v>-8.435213005479941</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.229846400839913</v>
+        <v>-0.2214761689783913</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.876673969025919</v>
+        <v>-1.855748389372116</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.026961076111782</v>
+        <v>2.039516423904063</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.323863111502858</v>
+        <v>-8.302937531849054</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1815687246405311</v>
+        <v>-0.1731984927790093</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.744398495395032</v>
+        <v>-1.72347291574123</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.101693847037341</v>
+        <v>2.114249194829622</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.133263436829704</v>
+        <v>-8.1123378571759</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1025137940836327</v>
+        <v>-0.0941435622221114</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.553798820721879</v>
+        <v>-1.532873241068077</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.218868712528869</v>
+        <v>2.23142406032115</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.884263638146123</v>
+        <v>-7.863338058492319</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.009992466613458095</v>
+        <v>0.01836269847497984</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.553798820721879</v>
+        <v>-1.532873241068077</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.231775053752528</v>
+        <v>2.244330401544809</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.989853627919228</v>
+        <v>-7.968928048265424</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1602194588950021</v>
+        <v>-0.1518492270334804</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.659388810494984</v>
+        <v>-1.638463230841181</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.040445130289446</v>
+        <v>2.053000478081728</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.008588530037825</v>
+        <v>-7.987662950384021</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1191690778653545</v>
+        <v>-0.1107988460038332</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.659388810494984</v>
+        <v>-1.638463230841181</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.088989472166533</v>
+        <v>2.101544819958814</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.860648488630225</v>
+        <v>-7.839722908976421</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1798719839904823</v>
+        <v>-0.171501752128961</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.639067894586426</v>
+        <v>-1.618142314932624</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.9813030990235</v>
+        <v>1.993858446815781</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.836419852241253</v>
+        <v>-7.815494272587449</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1788945156883717</v>
+        <v>-0.1705242838268499</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.614839258197454</v>
+        <v>-1.593913678543651</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.987126294603405</v>
+        <v>1.999681642395687</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.792871445470563</v>
+        <v>-7.771945865816758</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1684357650751886</v>
+        <v>-0.1600655332136669</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.614839258197454</v>
+        <v>-1.593913678543651</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.980165682508312</v>
+        <v>1.992721030300594</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.550723052016704</v>
+        <v>-7.5297974723629</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.0571140533125023</v>
+        <v>-0.04874382145098055</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.614839258197454</v>
+        <v>-1.593913678543651</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.994628036889455</v>
+        <v>2.007183384681737</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.487493680248356</v>
+        <v>-7.466568100594552</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.03729018414596785</v>
+        <v>-0.0289199522844461</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.614839258197454</v>
+        <v>-1.593913678543651</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.98916015734865</v>
+        <v>2.001715505140932</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.364202545431225</v>
+        <v>-7.343276965777421</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.009524363791461266</v>
+        <v>0.01789459565298301</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.491548123380324</v>
+        <v>-1.470622543726521</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.060632932249505</v>
+        <v>2.073188280041787</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.343053346527782</v>
+        <v>-7.322127766873978</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.02568502159016361</v>
+        <v>0.03405525345168536</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.47039892447688</v>
+        <v>-1.449473344823077</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.081023429828896</v>
+        <v>2.093578777621178</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.099287904544338</v>
+        <v>-7.078362324890533</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1189719067305921</v>
+        <v>0.1273421385921139</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.47039892447688</v>
+        <v>-1.449473344823077</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.076804138175947</v>
+        <v>2.089359485968228</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.835259837351078</v>
+        <v>-6.814334257697274</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2267074475279118</v>
+        <v>0.2350776793894336</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.268533525660927</v>
+        <v>-1.247607946007124</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.200047691385535</v>
+        <v>2.212603039177817</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.585409443402003</v>
+        <v>-6.564483863748199</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3193896800912439</v>
+        <v>0.3277599119527657</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.268533525660927</v>
+        <v>-1.247607946007124</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.192789766369237</v>
+        <v>2.205345114161519</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.409517350934571</v>
+        <v>-6.388591771280767</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3933456405988656</v>
+        <v>0.4017158724603873</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.268533525660927</v>
+        <v>-1.247607946007124</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.196388889889886</v>
+        <v>2.208944237682168</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.238070887912108</v>
+        <v>-6.217145308258304</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4752517318624045</v>
+        <v>0.4836219637239263</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.097087062638463</v>
+        <v>-1.076161482984661</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.312584273757917</v>
+        <v>2.325139621550199</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.013037888243285</v>
+        <v>-5.992112308589481</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5642854093462306</v>
+        <v>0.5726556412077524</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8720540629696406</v>
+        <v>-0.8511284833158378</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.446624551175508</v>
+        <v>2.45917989896779</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.798403510606878</v>
+        <v>-5.777477930953074</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6548339614551111</v>
+        <v>0.6632041933166324</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6574196853332338</v>
+        <v>-0.636494105679431</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.58009997881167</v>
+        <v>2.592655326603951</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.70540346940098</v>
+        <v>-5.684477889747176</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6732282367212656</v>
+        <v>0.6815984685827874</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6574196853332338</v>
+        <v>-0.636494105679431</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.561294237595465</v>
+        <v>2.573849585387747</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.46497297259612</v>
+        <v>-5.444047392942315</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7711435120680874</v>
+        <v>0.7795137439296091</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4169891885283735</v>
+        <v>-0.3960636088745707</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.707295612303259</v>
+        <v>2.71985096009554</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.392730404424925</v>
+        <v>-5.371804824771121</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8039698531713855</v>
+        <v>0.8123400850329072</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4169891885283735</v>
+        <v>-0.3960636088745707</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.711224926138079</v>
+        <v>2.723780273930361</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.27679055479974</v>
+        <v>-5.255864975145935</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8510243769387995</v>
+        <v>0.8593946088003213</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3401674575122496</v>
+        <v>-0.3192418778584468</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.757996548665093</v>
+        <v>2.770551896457375</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.034134966376577</v>
+        <v>-5.013209386722773</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9450846835280582</v>
+        <v>0.9534549153895799</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3401674575122496</v>
+        <v>-0.3192418778584468</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.754994619885087</v>
+        <v>2.767549967677368</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.814114168339566</v>
+        <v>-4.793188588685762</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.034672039753477</v>
+        <v>1.043042271614998</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.1989476124442694</v>
+        <v>-0.1780220327904666</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.841305563936489</v>
+        <v>2.853860911728771</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.681246479276289</v>
+        <v>-4.660320899622485</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.103713298180611</v>
+        <v>1.112083530042133</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.1989476124442694</v>
+        <v>-0.1780220327904666</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.857199746738312</v>
+        <v>2.869755094530594</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966259</v>
+        <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.521731375756919</v>
+        <v>-4.500805796103115</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.168665184028661</v>
+        <v>1.177035415890182</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.03943250892489947</v>
+        <v>-0.01850692927109665</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.954054653290236</v>
+        <v>2.966610001082518</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046996</v>
+        <v>3.791269976046997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.377059230657181</v>
+        <v>-4.356133651003377</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.236622144629995</v>
+        <v>1.244992376491517</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.1052396361748379</v>
+        <v>0.1261652158286408</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.050946042911518</v>
+        <v>3.0635013907038</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412103</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.436934058014874</v>
+        <v>-4.41600847836107</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.198709705088344</v>
+        <v>1.207079936949866</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.04536480881714583</v>
+        <v>0.06629038847094865</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.001058637898329</v>
+        <v>3.013613985690611</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144516</v>
+        <v>3.762643902144517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.350134560235865</v>
+        <v>-4.329208980582061</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.255829997522514</v>
+        <v>1.264200229384036</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.04536480881714583</v>
+        <v>0.06629038847094865</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.023459131220895</v>
+        <v>3.036014479013177</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.352604266697671</v>
+        <v>-4.331678687043867</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.254914516311203</v>
+        <v>1.263284748172725</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.04289510235533966</v>
+        <v>0.06382068200914248</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.022049708717224</v>
+        <v>3.034605056509505</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.420974453021682</v>
+        <v>-4.400048873367878</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.238573364256301</v>
+        <v>1.246943596117823</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.05217080139155461</v>
+        <v>0.07309638104535743</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.038622050613654</v>
+        <v>3.051177398405936</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.299558023395205</v>
+        <v>-4.278632443741401</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.277576644738783</v>
+        <v>1.285946876600305</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.05217080139155461</v>
+        <v>0.07309638104535743</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.029058759245546</v>
+        <v>3.041614107037828</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887703</v>
+        <v>3.710903155887705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.33055118272391</v>
+        <v>-4.309625603070106</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.089888946047688</v>
+        <v>1.09825917790921</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.05217080139155461</v>
+        <v>0.07309638104535743</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.853768324285932</v>
+        <v>2.866323672078214</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675901</v>
+        <v>3.746038950675903</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.155076922931441</v>
+        <v>-4.134151343277637</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.164645881956464</v>
+        <v>1.173016113817985</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.05217080139155461</v>
+        <v>0.07309638104535743</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.85833555627772</v>
+        <v>2.870890904070002</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695446</v>
+        <v>3.765020747695448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.26601317557269</v>
+        <v>-4.245087595918886</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.096013409661171</v>
+        <v>1.104383641522693</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.05217080139155461</v>
+        <v>0.07309638104535743</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.834077585038927</v>
+        <v>2.846632932831209</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581291</v>
+        <v>3.773206721581293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.469039753115923</v>
+        <v>-4.448114173462119</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.017934163863783</v>
+        <v>1.026304395725305</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1508557761516788</v>
+        <v>-0.129930196497876</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.715393023732893</v>
+        <v>2.727948371525175</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434037673416</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.31111415418063</v>
+        <v>-4.290188574526826</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.091276789870033</v>
+        <v>1.099647021731555</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1508557761516788</v>
+        <v>-0.129930196497876</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.725565410165025</v>
+        <v>2.738120757957307</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212296</v>
+        <v>3.786946382212298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.459435407991759</v>
+        <v>-4.438509828337954</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.026894558919442</v>
+        <v>1.035264790780964</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1508557761516788</v>
+        <v>-0.129930196497876</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.720511680738885</v>
+        <v>2.733067028531167</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.460618492642819</v>
+        <v>-4.439692912989015</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.018197100503543</v>
+        <v>1.026567332365065</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1564988246181903</v>
+        <v>-0.1355732449643875</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.708901627103504</v>
+        <v>2.721456974895786</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.337490785648736</v>
+        <v>-4.316565205994932</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.068000056334278</v>
+        <v>1.076370288195799</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1564988246181903</v>
+        <v>-0.1355732449643875</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.709453500136606</v>
+        <v>2.722008847928887</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279498</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.244680304197876</v>
+        <v>-4.223754724544072</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.034396940805987</v>
+        <v>1.042767172667509</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.06368834316733096</v>
+        <v>-0.04276276351352815</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.694412480898487</v>
+        <v>2.706967828690769</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.196117251976847</v>
+        <v>-4.175191672323042</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.055695637619</v>
+        <v>1.064065869480522</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.01512529094630077</v>
+        <v>0.005800288707502044</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.725423788155706</v>
+        <v>2.737979135947988</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.083446033740596</v>
+        <v>-4.062520454086792</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.095839833425223</v>
+        <v>1.104210065286745</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.09754592728994943</v>
+        <v>0.1184715069437522</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.788102227609179</v>
+        <v>2.800657575401461</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268535</v>
+        <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.971069032557924</v>
+        <v>-3.95014345290412</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.146281929728959</v>
+        <v>1.154652161590481</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.09754592728994943</v>
+        <v>0.1184715069437522</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.793593523439846</v>
+        <v>2.806148871232128</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968861</v>
+        <v>3.689594264968863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.169303601444654</v>
+        <v>-4.14837802179085</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.078485303942806</v>
+        <v>1.086855535804328</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1006886415967811</v>
+        <v>-0.07976306194297833</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.686149983876347</v>
+        <v>2.698705331668629</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175321</v>
+        <v>3.643066046175323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.252304882469933</v>
+        <v>-4.231379302816129</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8836405115333481</v>
+        <v>0.8920107433948699</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1192595261239549</v>
+        <v>-0.09833394647015209</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.513363173160696</v>
+        <v>2.525918520952978</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199268</v>
+        <v>3.68271273519927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.093110610413357</v>
+        <v>-4.072185030759552</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.067467881075185</v>
+        <v>1.075838112936706</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1192595261239549</v>
+        <v>-0.09833394647015209</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.633512833879902</v>
+        <v>2.646068181672183</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660768</v>
+        <v>3.73300886566077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.179709193394459</v>
+        <v>-4.158783613740655</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.047341473985066</v>
+        <v>1.055711705846588</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1192595261239549</v>
+        <v>-0.09833394647015209</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.648025859982225</v>
+        <v>2.660581207774506</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.141325530836308</v>
+        <v>-4.120399951182504</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.060114380350695</v>
+        <v>1.068484612212217</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.08087586356580373</v>
+        <v>-0.05995028391200091</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.668475498859484</v>
+        <v>2.681030846651766</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002484</v>
+        <v>3.751143622002486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.964209200801142</v>
+        <v>-3.943283621147338</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.127689941210064</v>
+        <v>1.136060173071585</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.08087586356580373</v>
+        <v>-0.05995028391200091</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.665204527704786</v>
+        <v>2.677759875497068</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263902</v>
+        <v>3.741324873263904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.934507076824849</v>
+        <v>-3.913581497171045</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.140254182562494</v>
+        <v>1.148624414424016</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.0853459887811171</v>
+        <v>-0.06442040912731428</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.663205844337511</v>
+        <v>2.675761192129793</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481236</v>
+        <v>3.750725801481238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.755131655586081</v>
+        <v>-3.734206075932277</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.205791326364416</v>
+        <v>1.214161558225937</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.07143076938960158</v>
+        <v>0.0923563490434044</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.751058874546357</v>
+        <v>2.763614222338638</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452231</v>
+        <v>3.716988143452233</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.800145869106687</v>
+        <v>-3.779220289452883</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.168593096287763</v>
+        <v>1.176963328149285</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.04108187407499697</v>
+        <v>0.06200745372879979</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.713656992689184</v>
+        <v>2.726212340481465</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979538</v>
+        <v>3.73702303297954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.067150379379123</v>
+        <v>-4.046224799725318</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.067482854517735</v>
+        <v>1.075853086379256</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1532811639679516</v>
+        <v>-0.1323555843141488</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.60273073220236</v>
+        <v>2.615286079994642</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230804</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.355937599838038</v>
+        <v>-4.335012020184234</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9511718882306699</v>
+        <v>0.9595421200921916</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.254367284066952</v>
+        <v>-0.2334417044131492</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.541282982039462</v>
+        <v>2.553838329831743</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,19 +46648,19 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.865304099770293</v>
+        <v>3.865304099770294</v>
       </c>
       <c r="C1961" t="n">
         <v>2.888901268509926</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.355937599838038</v>
+        <v>-4.335012020184234</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9511718882306699</v>
+        <v>0.9595421200921916</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.254367284066952</v>
+        <v>-0.2334417044131492</v>
       </c>
       <c r="G1961" t="n">
         <v>2.881965065496294</v>

--- a/tame_output/ON/bt/strategyON_20240511.xlsx
+++ b/tame_output/ON/bt/strategyON_20240511.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>28.0%</t>
         </is>
       </c>
     </row>
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.8%</t>
+          <t>132.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.7%</t>
+          <t>-52.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.6%</t>
+          <t>441.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,47 +1140,47 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.0%</t>
+          <t>-42.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>46.8%</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>-1.7%</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>46.3%</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-56.8%</t>
+          <t>-55.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.3%</t>
+          <t>-260.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.7%</t>
+          <t>-26.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-177.5%</t>
+          <t>-208.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-247.3%</t>
+          <t>-248.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-157.8%</t>
+          <t>-172.0%</t>
         </is>
       </c>
     </row>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.500805796103115</v>
+        <v>-4.515480304259899</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.177035415890182</v>
+        <v>1.171165612627469</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.01850692927109665</v>
+        <v>-0.03318143742788127</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.966610001082518</v>
+        <v>2.957805296188447</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.356133651003377</v>
+        <v>-4.370808159160162</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.244992376491517</v>
+        <v>1.239122573228803</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.1261652158286408</v>
+        <v>0.1114907076718561</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.0635013907038</v>
+        <v>3.054696685809729</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.41600847836107</v>
+        <v>-4.430682986517854</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.207079936949866</v>
+        <v>1.201210133687152</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.06629038847094865</v>
+        <v>0.05161588031416403</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.013613985690611</v>
+        <v>3.00480928079654</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.329208980582061</v>
+        <v>-4.343883488738845</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.264200229384036</v>
+        <v>1.258330426121322</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.06629038847094865</v>
+        <v>0.05161588031416403</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.036014479013177</v>
+        <v>3.027209774119106</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.331678687043867</v>
+        <v>-4.346353195200651</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.263284748172725</v>
+        <v>1.257414944910012</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.06382068200914248</v>
+        <v>0.04914617385235787</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.034605056509505</v>
+        <v>3.025800351615434</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.400048873367878</v>
+        <v>-4.414723381524661</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.246943596117823</v>
+        <v>1.24107379285511</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.07309638104535743</v>
+        <v>0.05842187288857281</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.051177398405936</v>
+        <v>3.042372693511865</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.278632443741401</v>
+        <v>-4.293306951898185</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.285946876600305</v>
+        <v>1.280077073337591</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.07309638104535743</v>
+        <v>0.05842187288857281</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.041614107037828</v>
+        <v>3.032809402143757</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.309625603070106</v>
+        <v>-4.32430011122689</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.09825917790921</v>
+        <v>1.092389374646496</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.07309638104535743</v>
+        <v>0.05842187288857281</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.866323672078214</v>
+        <v>2.857518967184143</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.134151343277637</v>
+        <v>-4.14882585143442</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.173016113817985</v>
+        <v>1.167146310555272</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.07309638104535743</v>
+        <v>0.05842187288857281</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.870890904070002</v>
+        <v>2.862086199175931</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.245087595918886</v>
+        <v>-4.259762104075669</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.104383641522693</v>
+        <v>1.098513838259979</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.07309638104535743</v>
+        <v>0.05842187288857281</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.846632932831209</v>
+        <v>2.837828227937139</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.448114173462119</v>
+        <v>-4.462788681618902</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.026304395725305</v>
+        <v>1.020434592462592</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.129930196497876</v>
+        <v>-0.1446047046546606</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.727948371525175</v>
+        <v>2.719143666631104</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.290188574526826</v>
+        <v>-4.304863082683609</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.099647021731555</v>
+        <v>1.093777218468841</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.129930196497876</v>
+        <v>-0.1446047046546606</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.738120757957307</v>
+        <v>2.729316053063236</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.438509828337954</v>
+        <v>-4.453184336494738</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.035264790780964</v>
+        <v>1.02939498751825</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.129930196497876</v>
+        <v>-0.1446047046546606</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.733067028531167</v>
+        <v>2.724262323637097</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.439692912989015</v>
+        <v>-4.454367421145799</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.026567332365065</v>
+        <v>1.020697529102351</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1355732449643875</v>
+        <v>-0.1502477531211721</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.721456974895786</v>
+        <v>2.712652270001715</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.316565205994932</v>
+        <v>-4.331239714151716</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.076370288195799</v>
+        <v>1.070500484933086</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1355732449643875</v>
+        <v>-0.1502477531211721</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.722008847928887</v>
+        <v>2.713204143034817</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.223754724544072</v>
+        <v>-4.238429232700856</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.042767172667509</v>
+        <v>1.036897369404796</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.04276276351352815</v>
+        <v>-0.05743727167031276</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.706967828690769</v>
+        <v>2.698163123796698</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.175191672323042</v>
+        <v>-4.189866180479826</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.064065869480522</v>
+        <v>1.058196066217808</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.005800288707502044</v>
+        <v>-0.008874219449282572</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.737979135947988</v>
+        <v>2.729174431053917</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.062520454086792</v>
+        <v>-4.077194962243576</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.104210065286745</v>
+        <v>1.098340262024031</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.1184715069437522</v>
+        <v>0.1037969987869676</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.800657575401461</v>
+        <v>2.79185287050739</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.95014345290412</v>
+        <v>-3.964817961060903</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.154652161590481</v>
+        <v>1.148782358327768</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.1184715069437522</v>
+        <v>0.1037969987869676</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.806148871232128</v>
+        <v>2.797344166338057</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.14837802179085</v>
+        <v>-4.163052529947634</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.086855535804328</v>
+        <v>1.080985732541615</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.07976306194297833</v>
+        <v>-0.09443757009976295</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.698705331668629</v>
+        <v>2.689900626774558</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.231379302816129</v>
+        <v>-4.246053810972913</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8920107433948699</v>
+        <v>0.8861409401321563</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.09833394647015209</v>
+        <v>-0.1130084546269367</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.525918520952978</v>
+        <v>2.517113816058907</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.072185030759552</v>
+        <v>-4.086859538916336</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.075838112936706</v>
+        <v>1.069968309673993</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.09833394647015209</v>
+        <v>-0.1130084546269367</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.646068181672183</v>
+        <v>2.637263476778112</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.158783613740655</v>
+        <v>-4.173458121897439</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.055711705846588</v>
+        <v>1.049841902583875</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.09833394647015209</v>
+        <v>-0.1130084546269367</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.660581207774506</v>
+        <v>2.651776502880435</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.120399951182504</v>
+        <v>-4.135074459339288</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.068484612212217</v>
+        <v>1.062614808949504</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.05995028391200091</v>
+        <v>-0.07462479206878553</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.681030846651766</v>
+        <v>2.672226141757695</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.943283621147338</v>
+        <v>-3.957958129304122</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.136060173071585</v>
+        <v>1.130190369808872</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.05995028391200091</v>
+        <v>-0.07462479206878553</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.677759875497068</v>
+        <v>2.668955170602997</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.913581497171045</v>
+        <v>-3.928256005327828</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.148624414424016</v>
+        <v>1.142754611161303</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.06442040912731428</v>
+        <v>-0.0790949172840989</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.675761192129793</v>
+        <v>2.666956487235722</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.734206075932277</v>
+        <v>-3.74888058408906</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.214161558225937</v>
+        <v>1.208291754963224</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.0923563490434044</v>
+        <v>0.07768184088661978</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.763614222338638</v>
+        <v>2.754809517444567</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.779220289452883</v>
+        <v>-3.793894797609667</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.176963328149285</v>
+        <v>1.171093524886571</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.06200745372879979</v>
+        <v>0.04733294557201517</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.726212340481465</v>
+        <v>2.717407635587394</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.046224799725318</v>
+        <v>-4.060899307882102</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.075853086379256</v>
+        <v>1.069983283116543</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1323555843141488</v>
+        <v>-0.1470300924709334</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.615286079994642</v>
+        <v>2.606481375100571</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.335012020184234</v>
+        <v>-4.349686528341017</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9595421200921916</v>
+        <v>0.9536723168294781</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2334417044131492</v>
+        <v>-0.2481162125699338</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.553838329831743</v>
+        <v>2.545033624937672</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.865304099770294</v>
+        <v>3.560571610792922</v>
       </c>
       <c r="C1961" t="n">
         <v>2.888901268509926</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.335012020184234</v>
+        <v>-4.33492484907716</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9595421200921916</v>
+        <v>1.154574904565315</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2334417044131492</v>
+        <v>-0.2481162125699338</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.881965065496294</v>
+        <v>2.740031540967966</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240511.xlsx
+++ b/tame_output/ON/bt/strategyON_20240511.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>59.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-41.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.8%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.2%</t>
+          <t>114.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.9%</t>
+          <t>134.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.6%</t>
+          <t>-54.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>441.1%</t>
+          <t>444.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-595.1%</t>
+          <t>-621.0%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1140,57 +1140,57 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.1%</t>
+          <t>-40.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>46.8%</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>-1.8%</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>46.3%</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-55.7%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-260.8%</t>
+          <t>-280.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-208.4%</t>
+          <t>-139.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-248.8%</t>
+          <t>-271.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,17 +1456,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-172.0%</t>
+          <t>-204.7%</t>
         </is>
       </c>
     </row>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705545</v>
+        <v>3.311607601705546</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045693</v>
+        <v>3.317575502045694</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386095</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998563</v>
+        <v>3.367370539998562</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082127</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760743</v>
+        <v>3.293766719760742</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706673</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201489</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.501052558539466</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.900257016592157</v>
+        <v>-10.09781873856928</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8285458921355775</v>
+        <v>-0.9075705809264289</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.039287846262815</v>
+        <v>-2.236849568239943</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.908340631057344</v>
+        <v>1.789803597871067</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.131913338815032</v>
+        <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.896566091635746</v>
+        <v>-10.13923474032736</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8270695221530135</v>
+        <v>-0.9212434253080874</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.039287846262815</v>
+        <v>-2.278265569998021</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.908340631057344</v>
+        <v>1.767847553137792</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.137426535933675</v>
+        <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.10082426696561</v>
+        <v>-10.34349291565723</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9032595951663165</v>
+        <v>-0.9974334983213904</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.166926790876804</v>
+        <v>-2.40590451461201</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.837270461407593</v>
+        <v>1.696777383488041</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.141909090418111</v>
+        <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.31886203859679</v>
+        <v>-10.5615306872884</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9859921493343511</v>
+        <v>-1.080166052489426</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.341697558972703</v>
+        <v>-2.580675282707909</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.736890555034489</v>
+        <v>1.596397477114938</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.157280791911532</v>
+        <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.24539220692934</v>
+        <v>-10.48806085562095</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9412325151739509</v>
+        <v>-1.035406418329025</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.268227727305255</v>
+        <v>-2.507205451040461</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.796344155528379</v>
+        <v>1.655851077608828</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.171836012659049</v>
+        <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.42051662431588</v>
+        <v>-10.6631852730075</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9967270613810513</v>
+        <v>-1.090900964536125</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.443352144691799</v>
+        <v>-2.682329868427005</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.70582472584397</v>
+        <v>1.565331647924418</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.164616847757453</v>
+        <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.65496871833037</v>
+        <v>-10.89763736702199</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.097727063888443</v>
+        <v>-1.191900967043517</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.443352144691799</v>
+        <v>-2.682329868427005</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.698605560942374</v>
+        <v>1.558112483022822</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480692492764399</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.157944656983477</v>
+        <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.94277256286761</v>
+        <v>-11.18544121155923</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.219520792477315</v>
+        <v>-1.313694695632389</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.731155989229037</v>
+        <v>-2.970133712964243</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.519251063446055</v>
+        <v>1.378757985526503</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493716014390588</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.159060446822033</v>
+        <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.17259701003143</v>
+        <v>-11.41526565872305</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.310334781504288</v>
+        <v>-1.404508684659363</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.893803526299197</v>
+        <v>-3.132781250034403</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.422778331042515</v>
+        <v>1.282285253122963</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492101641297402</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.161754175451148</v>
+        <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.4046259297677</v>
+        <v>-11.64729457845931</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.400452620769678</v>
+        <v>-1.494626523924753</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.95581622348762</v>
+        <v>-3.194793947222827</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.388264441358576</v>
+        <v>1.247771363439024</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.165744511137548</v>
+        <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.35261041579888</v>
+        <v>-11.5952790644905</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.375656079495752</v>
+        <v>-1.469829982650826</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.95581622348762</v>
+        <v>-3.194793947222827</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.392254777044976</v>
+        <v>1.251761699125425</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.164269284238807</v>
+        <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.494282257523</v>
+        <v>-11.73695090621462</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.433800043084142</v>
+        <v>-1.527973946239216</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.95581622348762</v>
+        <v>-3.194793947222827</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.390779550146235</v>
+        <v>1.250286472226683</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.179322694403679</v>
+        <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.44469141309817</v>
+        <v>-11.68736006178979</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.398910295149336</v>
+        <v>-1.49308419830441</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.906225379062787</v>
+        <v>-3.145203102797993</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.435587466966007</v>
+        <v>1.295094389046456</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.166271560756996</v>
+        <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.24553930586107</v>
+        <v>-11.48820795455269</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.33230058590118</v>
+        <v>-1.426474489056254</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.740902853112973</v>
+        <v>-2.97988057684818</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.521729848889212</v>
+        <v>1.381236770969661</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.175850633793205</v>
+        <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.01969415314166</v>
+        <v>-11.26236280183328</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.232383451777207</v>
+        <v>-1.326557354932282</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.69897617752581</v>
+        <v>-2.937953901261016</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.556464927277719</v>
+        <v>1.415971849358168</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684843823812106</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.176989778349264</v>
+        <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.89511549680407</v>
+        <v>-11.13778414549568</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.181412844686112</v>
+        <v>-1.275586747841186</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.69897617752581</v>
+        <v>-2.937953901261016</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.557604071833778</v>
+        <v>1.417110993914227</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710935533646221</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.179623552511371</v>
+        <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.94801078484836</v>
+        <v>-11.19067943353997</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.199937185741718</v>
+        <v>-1.294111088896792</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.694020831437363</v>
+        <v>-2.93299855517257</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.563211053648953</v>
+        <v>1.422717975729402</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768951674611572</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.185357256750008</v>
+        <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.66410205391961</v>
+        <v>-10.90677070261122</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.080639989131583</v>
+        <v>-1.174813892286656</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.694020831437363</v>
+        <v>-2.93299855517257</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.56894475788759</v>
+        <v>1.428451679968038</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728577929955332</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.175619994356143</v>
+        <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.59273566130996</v>
+        <v>-10.83540431000158</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.061830694481588</v>
+        <v>-1.156004597636663</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.622654438827716</v>
+        <v>-2.861632162562922</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.602027331059513</v>
+        <v>1.461534253139962</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747702660232416</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.165736513043235</v>
+        <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.32889879410589</v>
+        <v>-10.57156744279751</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9661794289128678</v>
+        <v>-1.060353332067943</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.622654438827716</v>
+        <v>-2.861632162562922</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.592143849746606</v>
+        <v>1.451650771827054</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766317079436232</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.163901952543861</v>
+        <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.06165699323749</v>
+        <v>-10.30432564192911</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.861117269064883</v>
+        <v>-0.9552911722199569</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.622654438827716</v>
+        <v>-2.861632162562922</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.590309289247232</v>
+        <v>1.44981621132768</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784684521311952</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.1636016375704</v>
+        <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.963749954561001</v>
+        <v>-10.20641860325262</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8222547685677473</v>
+        <v>-0.9164286717228216</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.554668688967159</v>
+        <v>-2.793646412702365</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.630800424190105</v>
+        <v>1.490307346270554</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800829354097248</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.164270143715894</v>
+        <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.939796413585043</v>
+        <v>-10.18246506227666</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8120048460318707</v>
+        <v>-0.9061787491869446</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.530715147991202</v>
+        <v>-2.769692871726408</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.645841054921173</v>
+        <v>1.505347977001622</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789311112017777</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.151009827554142</v>
+        <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.675736475262246</v>
+        <v>-9.918405123953862</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7196411868645041</v>
+        <v>-0.8138150900195784</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.266655209668406</v>
+        <v>-2.505632933403612</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.791016701753099</v>
+        <v>1.650523623833547</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.83325274783973</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.148222793893841</v>
+        <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.968656851757409</v>
+        <v>-9.211325500449025</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4395963711228701</v>
+        <v>-0.533770274277944</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.266655209668406</v>
+        <v>-2.505632933403612</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.788229668092798</v>
+        <v>1.647736590173246</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839374447388733</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.148566417781682</v>
+        <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.928472553391218</v>
+        <v>-9.171141202082834</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4231790278885526</v>
+        <v>-0.5173529310436265</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.226470911302215</v>
+        <v>-2.465448635037421</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.812683871000354</v>
+        <v>1.672190793080802</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856161751626479</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.147933239002439</v>
+        <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.848402757853414</v>
+        <v>-9.09107140654503</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3917842884526737</v>
+        <v>-0.485958191607748</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.146401115764411</v>
+        <v>-2.385378839499617</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.860092569543793</v>
+        <v>1.719599491624241</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.155857667840292</v>
+        <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.614921535623814</v>
+        <v>-8.857590184315431</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2904673707229817</v>
+        <v>-0.3846412738780556</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.912919893534812</v>
+        <v>-2.151897617270019</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.008105731719405</v>
+        <v>1.867612653799853</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.152965457527332</v>
+        <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.435213005479941</v>
+        <v>-8.677881654171557</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2214761689783913</v>
+        <v>-0.3156500721334656</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.855748389372116</v>
+        <v>-2.094726113107323</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.039516423904063</v>
+        <v>1.899023345984511</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.14833294427436</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.302937531849054</v>
+        <v>-8.54560618054067</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1731984927790093</v>
+        <v>-0.2673723959340837</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.72347291574123</v>
+        <v>-1.962450639476436</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.114249194829622</v>
+        <v>1.97375611691007</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784718794105956</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.151148004961996</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.1123378571759</v>
+        <v>-8.355006505867516</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.0941435622221114</v>
+        <v>-0.1883174653771853</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.532873241068077</v>
+        <v>-1.771850964803283</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.23142406032115</v>
+        <v>2.090930982401598</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753882571960991</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.164054346185655</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.863338058492319</v>
+        <v>-8.106006707183935</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.01836269847497984</v>
+        <v>-0.0758112046800945</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.532873241068077</v>
+        <v>-1.771850964803283</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.244330401544809</v>
+        <v>2.103837323625258</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692931855607648</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.036078416586436</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.968928048265424</v>
+        <v>-8.21159669695704</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1518492270334804</v>
+        <v>-0.2460231301885547</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.638463230841181</v>
+        <v>-1.877440954576387</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.053000478081728</v>
+        <v>1.912507400162176</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770422583987906</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.084622758463523</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.987662950384021</v>
+        <v>-8.230331599075637</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1107988460038332</v>
+        <v>-0.2049727491589071</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.638463230841181</v>
+        <v>-1.877440954576387</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.101544819958814</v>
+        <v>1.961051742039262</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.964743835775355</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.839722908976421</v>
+        <v>-8.082391557668037</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.171501752128961</v>
+        <v>-0.2656756552840349</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.618142314932624</v>
+        <v>-1.85712003866783</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.993858446815781</v>
+        <v>1.853365368896229</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.956029849521877</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.815494272587449</v>
+        <v>-8.058162921279065</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1705242838268499</v>
+        <v>-0.2646981869819243</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.593913678543651</v>
+        <v>-1.832891402278858</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.999681642395687</v>
+        <v>1.859188564476135</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.949069237426784</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.771945865816758</v>
+        <v>-8.014614514508374</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1600655332136669</v>
+        <v>-0.2542394363687408</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.593913678543651</v>
+        <v>-1.832891402278858</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.992721030300594</v>
+        <v>1.852227952381041</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.963531591807927</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.5297974723629</v>
+        <v>-7.772466121054515</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.04874382145098055</v>
+        <v>-0.1429177246060545</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.593913678543651</v>
+        <v>-1.832891402278858</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.007183384681737</v>
+        <v>1.866690306762185</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.958063712267122</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.466568100594552</v>
+        <v>-7.709236749286167</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.0289199522844461</v>
+        <v>-0.12309385543952</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.593913678543651</v>
+        <v>-1.832891402278858</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.001715505140932</v>
+        <v>1.86122242722138</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.82805292879205</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.955561806277699</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.343276965777421</v>
+        <v>-7.585945614469036</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.01789459565298301</v>
+        <v>-0.07627930750209089</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.470622543726521</v>
+        <v>-1.709600267461727</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.073188280041787</v>
+        <v>1.932695202122235</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812453678919912</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.963262784515024</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.322127766873978</v>
+        <v>-7.564796415565593</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.03405525345168536</v>
+        <v>-0.06011864970338854</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.449473344823077</v>
+        <v>-1.688451068558284</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.093578777621178</v>
+        <v>1.953085699701626</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748328408318097</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.959043492862075</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.078362324890533</v>
+        <v>-7.321030973582149</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1273421385921139</v>
+        <v>0.03316823543703995</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.449473344823077</v>
+        <v>-1.688451068558284</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.089359485968228</v>
+        <v>1.948866408048676</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824311233057528</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.961167806782091</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.814334257697274</v>
+        <v>-7.057002906388888</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2350776793894336</v>
+        <v>0.1409037762343601</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.247607946007124</v>
+        <v>-1.486585669742331</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.212603039177817</v>
+        <v>2.072109961258265</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.953909881765793</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.564483863748199</v>
+        <v>-6.807152512439814</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3277599119527657</v>
+        <v>0.2335860087976922</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.247607946007124</v>
+        <v>-1.486585669742331</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.205345114161519</v>
+        <v>2.064852036241967</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.957509005286441</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.388591771280767</v>
+        <v>-6.631260419972381</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4017158724603873</v>
+        <v>0.3075419693053139</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.247607946007124</v>
+        <v>-1.486585669742331</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.208944237682168</v>
+        <v>2.068451159762616</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.78093391139299</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.970836511340995</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.217145308258304</v>
+        <v>-6.459813956949918</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4836219637239263</v>
+        <v>0.3894480605688528</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.076161482984661</v>
+        <v>-1.315139206719867</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.325139621550199</v>
+        <v>2.184646543630647</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773765222632784</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.969856988957292</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.992112308589481</v>
+        <v>-6.234780957281095</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5726556412077524</v>
+        <v>0.4784817380526789</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8511284833158378</v>
+        <v>-1.090106207051044</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.45917989896779</v>
+        <v>2.318686821048238</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353074</v>
+        <v>3.764617879883076</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.974551790011609</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.777477930953074</v>
+        <v>-6.020146579644688</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6632041933166324</v>
+        <v>0.5690302901615589</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.636494105679431</v>
+        <v>-0.8754718294146375</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.592655326603951</v>
+        <v>2.452162248684399</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544783</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.955746048795405</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.684477889747176</v>
+        <v>-5.92714653843879</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6815984685827874</v>
+        <v>0.5874245654277139</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.636494105679431</v>
+        <v>-0.8754718294146375</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.573849585387747</v>
+        <v>2.433356507468195</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712294</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.957489125420282</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.444047392942315</v>
+        <v>-5.68671604163393</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7795137439296091</v>
+        <v>0.6853398407745352</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.3960636088745707</v>
+        <v>-0.6350413326097772</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.71985096009554</v>
+        <v>2.579357882175989</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837686</v>
+        <v>3.821593509367688</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.961418439255103</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.371804824771121</v>
+        <v>-5.614473473462735</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8123400850329072</v>
+        <v>0.7181661818778333</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.3960636088745707</v>
+        <v>-0.6350413326097772</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.723780273930361</v>
+        <v>2.583287196010809</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349967</v>
+        <v>3.822326997879969</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.962097023172443</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.255864975145935</v>
+        <v>-5.49853362383755</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8593946088003213</v>
+        <v>0.7652207056452478</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3192418778584468</v>
+        <v>-0.5582196015936534</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.770551896457375</v>
+        <v>2.630058818537823</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972341</v>
+        <v>3.848616626502343</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.959095094392436</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.013209386722773</v>
+        <v>-5.255878035414387</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9534549153895799</v>
+        <v>0.859281012234506</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3192418778584468</v>
+        <v>-0.5582196015936534</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.767549967677368</v>
+        <v>2.627056889757816</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866537614594</v>
+        <v>3.818668951675942</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.96067413140305</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.793188588685762</v>
+        <v>-5.035857237377376</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.043042271614998</v>
+        <v>0.9488683684599244</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.1780220327904666</v>
+        <v>-0.4169997565256731</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.853860911728771</v>
+        <v>2.713367833809219</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009952</v>
+        <v>3.843274527539954</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.976568314204874</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.660320899622485</v>
+        <v>-4.902989548314099</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.112083530042133</v>
+        <v>1.017909626887059</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.1780220327904666</v>
+        <v>-0.4169997565256731</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.869755094530594</v>
+        <v>2.729262016611042</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.977714158645175</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.515480304259899</v>
+        <v>-4.743474444794729</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.171165612627469</v>
+        <v>1.082861512735109</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.03318143742788127</v>
+        <v>-0.2574846530063032</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.957805296188447</v>
+        <v>2.826116923162966</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046997</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.987802261206615</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.370808159160162</v>
+        <v>-4.598802299694992</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.239122573228803</v>
+        <v>1.150818473336443</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.1114907076718561</v>
+        <v>-0.1128125079065658</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.054696685809729</v>
+        <v>2.923008312784248</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.973839752608041</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.430682986517854</v>
+        <v>-4.658677127052684</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.201210133687152</v>
+        <v>1.112906033794792</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.05161588031416403</v>
+        <v>-0.1726873352642579</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.00480928079654</v>
+        <v>2.873120907771059</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144517</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.996240245930607</v>
+        <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.343883488738845</v>
+        <v>-4.571877629273676</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.258330426121322</v>
+        <v>1.170026326228962</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.05161588031416403</v>
+        <v>-0.1726873352642579</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.027209774119106</v>
+        <v>2.895521401093625</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.996312647304019</v>
+        <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.346353195200651</v>
+        <v>-4.574347335735482</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.257414944910012</v>
+        <v>1.169110845017652</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.04914617385235787</v>
+        <v>-0.1751570417260641</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.025800351615434</v>
+        <v>2.894111978589953</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473602</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.007319569778721</v>
+        <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.414723381524661</v>
+        <v>-4.642717522059492</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.24107379285511</v>
+        <v>1.15276969296275</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.05842187288857281</v>
+        <v>-0.1658813426898491</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.042372693511865</v>
+        <v>2.910684320486384</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978371</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.997756278410613</v>
+        <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.293306951898185</v>
+        <v>-4.521301092433015</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.280077073337591</v>
+        <v>1.191772973445231</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.05842187288857281</v>
+        <v>-0.1658813426898491</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.032809402143757</v>
+        <v>2.901121029118276</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887705</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.822465843450999</v>
+        <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.32430011122689</v>
+        <v>-4.552294251761721</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.092389374646496</v>
+        <v>1.004085274754136</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.05842187288857281</v>
+        <v>-0.1658813426898491</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.857518967184143</v>
+        <v>2.725830594158662</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675903</v>
+        <v>3.746042526205903</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.827033075442787</v>
+        <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.14882585143442</v>
+        <v>-4.376819991969251</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.167146310555272</v>
+        <v>1.078842210662912</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.05842187288857281</v>
+        <v>-0.1658813426898491</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.862086199175931</v>
+        <v>2.73039782615045</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695448</v>
+        <v>3.765024323225448</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.802775104203994</v>
+        <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.259762104075669</v>
+        <v>-4.4877562446105</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.098513838259979</v>
+        <v>1.010209738367619</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.05842187288857281</v>
+        <v>-0.1658813426898491</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.837828227937139</v>
+        <v>2.706139854911657</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581293</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.8059064894239</v>
+        <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.462788681618902</v>
+        <v>-4.690782822153733</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.020434592462592</v>
+        <v>0.9321304925702316</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1446047046546606</v>
+        <v>-0.3689079202330825</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.719143666631104</v>
+        <v>2.587455293605623</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.816078875856032</v>
+        <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.304863082683609</v>
+        <v>-4.53285722321844</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.093777218468841</v>
+        <v>1.005473118576481</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1446047046546606</v>
+        <v>-0.3689079202330825</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.729316053063236</v>
+        <v>2.597627680037755</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212298</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.811025146429893</v>
+        <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.453184336494738</v>
+        <v>-4.451236493353692</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.02939498751825</v>
+        <v>1.033067681096241</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1446047046546606</v>
+        <v>-0.3689079202330825</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.724262323637097</v>
+        <v>2.592573950611615</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.802800921874418</v>
+        <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.454367421145799</v>
+        <v>-4.452419578004752</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.020697529102351</v>
+        <v>1.024370222680342</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1502477531211721</v>
+        <v>-0.374550968699594</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.712652270001715</v>
+        <v>2.580963896976234</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.80335279490752</v>
+        <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.331239714151716</v>
+        <v>-4.329291871010669</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.070500484933086</v>
+        <v>1.074173178511077</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1502477531211721</v>
+        <v>-0.374550968699594</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.713204143034817</v>
+        <v>2.581515770009336</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.732625486798885</v>
+        <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.238429232700856</v>
+        <v>-4.23648138955981</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.036897369404796</v>
+        <v>1.040570062982786</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.05743727167031276</v>
+        <v>-0.2817404872487347</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.698163123796698</v>
+        <v>2.566474750771217</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.734498962723486</v>
+        <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.189866180479826</v>
+        <v>-4.18791833733878</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.058196066217808</v>
+        <v>1.061868759795799</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.008874219449282572</v>
+        <v>-0.2331774350277045</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.729174431053917</v>
+        <v>2.597486058028436</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.729574671235209</v>
+        <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.077194962243576</v>
+        <v>-4.07524711910253</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.098340262024031</v>
+        <v>1.102012955602022</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.1037969987869676</v>
+        <v>-0.1205062167914543</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.79185287050739</v>
+        <v>2.660164497481909</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.735065967065876</v>
+        <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.964817961060903</v>
+        <v>-3.962870117919857</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.148782358327768</v>
+        <v>1.152455051905758</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.1037969987869676</v>
+        <v>-0.1205062167914543</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.797344166338057</v>
+        <v>2.665655793312576</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968863</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.746563168834415</v>
+        <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.163052529947634</v>
+        <v>-4.161104686806588</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.080985732541615</v>
+        <v>1.084658426119605</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.09443757009976295</v>
+        <v>-0.3187407856781849</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.689900626774558</v>
+        <v>2.558212253749077</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175323</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.584918888835069</v>
+        <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.246053810972913</v>
+        <v>-4.244105967831866</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8861409401321563</v>
+        <v>0.889813633710147</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1130084546269367</v>
+        <v>-0.3373116702053586</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.517113816058907</v>
+        <v>2.385425443033426</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271273519927</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.705068549554274</v>
+        <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.086859538916336</v>
+        <v>-4.08491169577529</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.069968309673993</v>
+        <v>1.073641003251983</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1130084546269367</v>
+        <v>-0.3373116702053586</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.637263476778112</v>
+        <v>2.505575103752632</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73300886566077</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.719581575656597</v>
+        <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.173458121897439</v>
+        <v>-4.171510278756393</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.049841902583875</v>
+        <v>1.053514596161865</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1130084546269367</v>
+        <v>-0.3373116702053586</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.651776502880435</v>
+        <v>2.520088129854955</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383425</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.717001016998966</v>
+        <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.135074459339288</v>
+        <v>-4.133126616198242</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.062614808949504</v>
+        <v>1.066287502527494</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.07462479206878553</v>
+        <v>-0.2989280076472074</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.672226141757695</v>
+        <v>2.540537768732214</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002486</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.713730045844268</v>
+        <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.957958129304122</v>
+        <v>-3.956010286163075</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.130190369808872</v>
+        <v>1.133863063386863</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.07462479206878553</v>
+        <v>-0.2989280076472074</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.668955170602997</v>
+        <v>2.537266797577516</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263904</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.714413437606181</v>
+        <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.928256005327828</v>
+        <v>-3.926308162186782</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.142754611161303</v>
+        <v>1.146427304739293</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.0790949172840989</v>
+        <v>-0.3033981328625208</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.666956487235722</v>
+        <v>2.535268114210241</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481238</v>
+        <v>3.750729377011238</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.708200412912595</v>
+        <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.74888058408906</v>
+        <v>-3.746932740948014</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.208291754963224</v>
+        <v>1.211964448541215</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.07768184088661978</v>
+        <v>-0.1466213746918021</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.754809517444567</v>
+        <v>2.623121144419087</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452233</v>
+        <v>3.716991718982233</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.689007868244185</v>
+        <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.793894797609667</v>
+        <v>-3.79194695446862</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.171093524886571</v>
+        <v>1.174766218464562</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.04733294557201517</v>
+        <v>-0.1769702700064067</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.717407635587394</v>
+        <v>2.585719262561914</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702303297954</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.694699430583131</v>
+        <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.060899307882102</v>
+        <v>-4.058951464741056</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.069983283116543</v>
+        <v>1.073655976694533</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1470300924709334</v>
+        <v>-0.3713333080493553</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.606481375100571</v>
+        <v>2.47479300207509</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.704250609465734</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.693903352479632</v>
+        <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.349686528341017</v>
+        <v>-4.347738685199971</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9536723168294781</v>
+        <v>0.9573450104074688</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2481162125699338</v>
+        <v>-0.4724194281483557</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.545033624937672</v>
+        <v>2.413345251912191</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.560571610792922</v>
+        <v>3.877368507017945</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.888901268509926</v>
+        <v>2.696796908801204</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.33492484907716</v>
+        <v>-4.594004261816237</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.154574904565315</v>
+        <v>0.9573450104074688</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2481162125699338</v>
+        <v>-0.4724194281483557</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.740031540967966</v>
+        <v>2.413345251912191</v>
       </c>
     </row>
   </sheetData>
